--- a/data/trans_camb/P19C05-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P19C05-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,51; 3,58</t>
+          <t>-7,15; 3,21</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-10,92; -1,81</t>
+          <t>-11,06; -1,92</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-10,24; -1,44</t>
+          <t>-9,66; -1,04</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-10,59; -0,33</t>
+          <t>-10,52; -0,17</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-9,45; 0,8</t>
+          <t>-9,49; 1,58</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-11,02; -2,07</t>
+          <t>-10,6; -1,24</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-7,35; -0,21</t>
+          <t>-7,01; 0,51</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-8,59; -1,61</t>
+          <t>-9,0; -1,98</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-8,83; -2,61</t>
+          <t>-8,85; -2,75</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-44,11; 34,06</t>
+          <t>-44,44; 29,29</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-66,21; -14,1</t>
+          <t>-67,73; -14,85</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-60,62; -10,91</t>
+          <t>-58,48; -8,22</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-67,52; -2,07</t>
+          <t>-64,41; -0,59</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-60,3; 8,69</t>
+          <t>-59,93; 15,42</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-63,37; -18,62</t>
+          <t>-62,41; -12,6</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-46,65; -0,56</t>
+          <t>-45,44; 5,14</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-56,16; -13,57</t>
+          <t>-58,95; -16,32</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-55,93; -23,17</t>
+          <t>-55,68; -22,77</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 9,28</t>
+          <t>-1,74; 9,88</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,31; 3,18</t>
+          <t>-7,66; 2,92</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,42; 3,35</t>
+          <t>-5,65; 3,51</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,33; 5,16</t>
+          <t>-3,44; 5,1</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,05; 3,1</t>
+          <t>-4,59; 3,44</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-4,61; 2,72</t>
+          <t>-4,07; 3,0</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 6,67</t>
+          <t>-0,65; 6,26</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,87; 1,74</t>
+          <t>-5,08; 1,7</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-3,51; 2,19</t>
+          <t>-3,84; 2,46</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-11,82; 93,27</t>
+          <t>-12,96; 100,44</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-50,15; 35,11</t>
+          <t>-52,09; 28,94</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-38,6; 36,46</t>
+          <t>-38,65; 36,37</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-37,09; 87,03</t>
+          <t>-37,76; 97,49</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-51,83; 58,58</t>
+          <t>-50,92; 74,42</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-45,37; 48,98</t>
+          <t>-40,82; 53,81</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-6,49; 81,99</t>
+          <t>-6,75; 74,35</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-41,09; 21,24</t>
+          <t>-42,26; 20,93</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-30,06; 26,75</t>
+          <t>-31,3; 33,14</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 7,08</t>
+          <t>-2,19; 7,17</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 7,57</t>
+          <t>-2,06; 7,17</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-12,83; 0,88</t>
+          <t>-11,9; 1,13</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,99; 19,75</t>
+          <t>5,05; 19,84</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 15,09</t>
+          <t>-1,9; 14,74</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 12,52</t>
+          <t>-0,99; 12,51</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,85; 9,43</t>
+          <t>1,3; 9,12</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 7,6</t>
+          <t>-0,91; 7,88</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-9,52; 2,65</t>
+          <t>-9,89; 2,53</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-17,68; 68,56</t>
+          <t>-15,44; 67,07</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-13,95; 72,31</t>
+          <t>-13,66; 67,59</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-83,58; 7,79</t>
+          <t>-81,59; 8,82</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>37,17; 314,33</t>
+          <t>30,37; 308,45</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-16,91; 237,73</t>
+          <t>-16,04; 231,04</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-10,63; 196,59</t>
+          <t>-9,87; 198,89</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>13,0; 94,71</t>
+          <t>9,11; 89,17</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-3,86; 74,04</t>
+          <t>-6,08; 77,21</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-65,73; 23,81</t>
+          <t>-67,77; 22,83</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,6; 2,42</t>
+          <t>-4,6; 2,17</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-9,5; -2,66</t>
+          <t>-9,24; -2,69</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-8,43; -2,27</t>
+          <t>-8,94; -1,77</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,86; 3,58</t>
+          <t>-4,27; 3,6</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-9,38; -2,7</t>
+          <t>-9,54; -2,66</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-12,02; -3,05</t>
+          <t>-10,98; -2,82</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-3,67; 1,71</t>
+          <t>-3,64; 1,65</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-8,45; -3,64</t>
+          <t>-8,69; -3,48</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-9,69; -3,7</t>
+          <t>-9,9; -3,71</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-24,42; 15,39</t>
+          <t>-23,68; 13,62</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-47,67; -16,05</t>
+          <t>-46,57; -16,62</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-42,9; -14,65</t>
+          <t>-44,68; -11,24</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-25,6; 30,21</t>
+          <t>-26,65; 30,84</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-60,03; -21,17</t>
+          <t>-59,78; -21,45</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-73,49; -25,11</t>
+          <t>-71,96; -24,33</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-20,62; 11,96</t>
+          <t>-20,37; 11,44</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-47,77; -24,26</t>
+          <t>-48,44; -22,68</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-55,38; -24,95</t>
+          <t>-57,41; -25,57</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,33; 12,56</t>
+          <t>2,19; 13,22</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-6,66; 3,45</t>
+          <t>-6,32; 3,54</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-7,39; 1,87</t>
+          <t>-7,81; 1,8</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3,94; 13,62</t>
+          <t>3,18; 12,95</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-7,01; 2,14</t>
+          <t>-6,94; 2,54</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-8,06; 0,89</t>
+          <t>-8,1; 0,82</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,12; 11,48</t>
+          <t>3,94; 11,3</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-5,62; 1,11</t>
+          <t>-5,81; 0,93</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-6,57; 0,08</t>
+          <t>-6,82; 0,38</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>8,05; 147,59</t>
+          <t>12,95; 159,56</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-44,03; 41,92</t>
+          <t>-43,77; 44,64</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-49,17; 22,21</t>
+          <t>-50,66; 22,81</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>19,17; 102,52</t>
+          <t>17,17; 99,35</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-37,36; 16,31</t>
+          <t>-36,76; 19,09</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-42,31; 6,11</t>
+          <t>-43,27; 5,54</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>24,48; 92,41</t>
+          <t>24,26; 90,67</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-33,65; 9,14</t>
+          <t>-33,77; 7,87</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-40,16; 0,5</t>
+          <t>-40,39; 2,62</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 5,79</t>
+          <t>-0,05; 5,81</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0,22; 6,03</t>
+          <t>0,15; 6,36</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 5,03</t>
+          <t>-1,44; 4,71</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-3,76; 4,06</t>
+          <t>-3,32; 4,12</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-10,59; -3,09</t>
+          <t>-10,89; -3,18</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-8,77; -1,8</t>
+          <t>-8,89; -2,07</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-2,9; 4,02</t>
+          <t>-2,79; 3,81</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-9,17; -2,85</t>
+          <t>-8,88; -2,41</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-7,81; -2,22</t>
+          <t>-8,18; -2,38</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-33,02; 1234,11</t>
+          <t>-38,37; —</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-23,25; 1291,61</t>
+          <t>-30,36; 1415,32</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-86,18; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-15,45; 19,73</t>
+          <t>-14,17; 20,11</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-44,69; -15,12</t>
+          <t>-45,93; -15,3</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-35,91; -8,72</t>
+          <t>-35,84; -9,96</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-14,71; 22,96</t>
+          <t>-14,08; 22,59</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-44,44; -15,3</t>
+          <t>-44,38; -15,07</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-39,41; -12,82</t>
+          <t>-39,85; -13,68</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 3,4</t>
+          <t>-0,78; 3,42</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-4,68; -0,96</t>
+          <t>-4,93; -1,07</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-6,69; -2,19</t>
+          <t>-6,47; -2,14</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>0,16; 4,01</t>
+          <t>-0,08; 3,98</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-6,56; -2,81</t>
+          <t>-6,45; -2,73</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-7,67; -3,25</t>
+          <t>-7,4; -3,2</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,99</t>
+          <t>0,29; 3,15</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-5,05; -2,49</t>
+          <t>-5,09; -2,46</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-6,14; -3,23</t>
+          <t>-6,3; -3,32</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-4,49; 26,78</t>
+          <t>-5,18; 27,07</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-32,21; -7,47</t>
+          <t>-32,92; -8,52</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-46,28; -17,11</t>
+          <t>-45,79; -17,26</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>0,85; 27,19</t>
+          <t>-0,77; 26,01</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-38,1; -18,56</t>
+          <t>-37,53; -17,9</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-45,73; -21,7</t>
+          <t>-44,24; -21,25</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>1,96; 20,71</t>
+          <t>1,72; 22,16</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-32,37; -17,02</t>
+          <t>-32,48; -17,3</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-40,02; -22,71</t>
+          <t>-40,97; -23,22</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P19C05-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P19C05-Clase-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-5,44</t>
+          <t>-5,27</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-5,85</t>
+          <t>-5,98</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-5,67</t>
+          <t>-5,64</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,15; 3,21</t>
+          <t>-6,7; 2,87</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-11,06; -1,92</t>
+          <t>-11,07; -1,72</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-9,66; -1,04</t>
+          <t>-9,91; -1,27</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-10,52; -0,17</t>
+          <t>-10,13; -0,06</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-9,49; 1,58</t>
+          <t>-9,67; 1,12</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-10,6; -1,24</t>
+          <t>-10,48; -2,04</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-7,01; 0,51</t>
+          <t>-7,56; -0,12</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-9,0; -1,98</t>
+          <t>-9,23; -2,25</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-8,85; -2,75</t>
+          <t>-8,53; -2,75</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-39,57%</t>
+          <t>-38,36%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-44,57%</t>
+          <t>-45,58%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-42,02%</t>
+          <t>-41,84%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-44,44; 29,29</t>
+          <t>-43,47; 24,94</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-67,73; -14,85</t>
+          <t>-66,79; -12,81</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-58,48; -8,22</t>
+          <t>-57,15; -10,96</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-64,41; -0,59</t>
+          <t>-65,02; 1,97</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-59,93; 15,42</t>
+          <t>-58,89; 12,13</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-62,41; -12,6</t>
+          <t>-62,85; -18,21</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-45,44; 5,14</t>
+          <t>-49,0; -0,34</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-58,95; -16,32</t>
+          <t>-58,58; -18,34</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-55,68; -22,77</t>
+          <t>-54,56; -23,4</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-1,09</t>
+          <t>-1,21</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-0,57</t>
+          <t>-0,68</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-0,5</t>
+          <t>-0,66</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 9,88</t>
+          <t>-1,66; 9,59</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,66; 2,92</t>
+          <t>-7,98; 2,92</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,65; 3,51</t>
+          <t>-6,14; 3,5</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,44; 5,1</t>
+          <t>-3,53; 5,3</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,59; 3,44</t>
+          <t>-5,11; 3,17</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-4,07; 3,0</t>
+          <t>-4,44; 2,56</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 6,26</t>
+          <t>-0,78; 6,27</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-5,08; 1,7</t>
+          <t>-4,62; 1,51</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-3,84; 2,46</t>
+          <t>-3,55; 2,16</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-8,59%</t>
+          <t>-9,57%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-7,42%</t>
+          <t>-8,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-4,99%</t>
+          <t>-6,56%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-12,96; 100,44</t>
+          <t>-12,28; 97,54</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-52,09; 28,94</t>
+          <t>-49,75; 30,94</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-38,65; 36,37</t>
+          <t>-39,45; 38,8</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-37,76; 97,49</t>
+          <t>-39,71; 94,4</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-50,92; 74,42</t>
+          <t>-53,09; 60,03</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-40,82; 53,81</t>
+          <t>-43,09; 45,51</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-6,75; 74,35</t>
+          <t>-6,85; 76,39</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-42,26; 20,93</t>
+          <t>-40,87; 19,01</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-31,3; 33,14</t>
+          <t>-30,12; 25,59</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-4,94</t>
+          <t>-0,66</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,21</t>
+          <t>6,3</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-2,58</t>
+          <t>1,21</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,19; 7,17</t>
+          <t>-2,12; 6,98</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 7,17</t>
+          <t>-1,94; 7,71</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-11,9; 1,13</t>
+          <t>-4,28; 3,83</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,05; 19,84</t>
+          <t>5,14; 19,85</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 14,74</t>
+          <t>-1,84; 14,56</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 12,51</t>
+          <t>-0,64; 12,87</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,3; 9,12</t>
+          <t>1,69; 9,0</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 7,88</t>
+          <t>-0,53; 7,79</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-9,89; 2,53</t>
+          <t>-2,66; 4,6</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-38,87%</t>
+          <t>-5,19%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>63,93%</t>
+          <t>64,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-21,51%</t>
+          <t>10,06%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-15,44; 67,07</t>
+          <t>-15,23; 66,57</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-13,66; 67,59</t>
+          <t>-13,55; 75,42</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-81,59; 8,82</t>
+          <t>-29,47; 35,3</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>30,37; 308,45</t>
+          <t>31,18; 311,96</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-16,04; 231,04</t>
+          <t>-18,22; 230,71</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-9,87; 198,89</t>
+          <t>-5,35; 219,03</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9,11; 89,17</t>
+          <t>13,57; 90,96</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-6,08; 77,21</t>
+          <t>-3,82; 79,75</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-67,77; 22,83</t>
+          <t>-19,12; 44,97</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-5,39</t>
+          <t>-4,97</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-6,31</t>
+          <t>-4,45</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-6,19</t>
+          <t>-4,86</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,6; 2,17</t>
+          <t>-4,97; 1,97</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-9,24; -2,69</t>
+          <t>-9,08; -2,36</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-8,94; -1,77</t>
+          <t>-8,16; -1,67</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,27; 3,6</t>
+          <t>-4,06; 3,47</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-9,54; -2,66</t>
+          <t>-9,59; -2,72</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-10,98; -2,82</t>
+          <t>-7,81; -1,46</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-3,64; 1,65</t>
+          <t>-3,61; 1,57</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-8,69; -3,48</t>
+          <t>-8,48; -3,65</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-9,9; -3,71</t>
+          <t>-7,27; -2,44</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-30,07%</t>
+          <t>-27,72%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-45,91%</t>
+          <t>-32,35%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-38,15%</t>
+          <t>-29,91%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-23,68; 13,62</t>
+          <t>-24,89; 12,3</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-46,57; -16,62</t>
+          <t>-46,73; -15,29</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-44,68; -11,24</t>
+          <t>-40,49; -9,83</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-26,65; 30,84</t>
+          <t>-25,63; 29,15</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-59,78; -21,45</t>
+          <t>-60,39; -22,35</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-71,96; -24,33</t>
+          <t>-48,9; -13,03</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-20,37; 11,44</t>
+          <t>-20,82; 10,52</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-48,44; -22,68</t>
+          <t>-47,95; -24,49</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-57,41; -25,57</t>
+          <t>-40,88; -15,96</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-2,4</t>
+          <t>-3,23</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-3,27</t>
+          <t>-1,58</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-2,95</t>
+          <t>-2,42</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,19; 13,22</t>
+          <t>2,38; 13,73</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-6,32; 3,54</t>
+          <t>-6,87; 3,83</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-7,81; 1,8</t>
+          <t>-8,16; 1,27</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3,18; 12,95</t>
+          <t>3,53; 13,84</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-6,94; 2,54</t>
+          <t>-6,66; 2,65</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-8,1; 0,82</t>
+          <t>-6,31; 2,17</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,94; 11,3</t>
+          <t>4,26; 11,59</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-5,81; 0,93</t>
+          <t>-5,51; 1,29</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-6,82; 0,38</t>
+          <t>-5,68; 0,51</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-21,35%</t>
+          <t>-28,75%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-20,09%</t>
+          <t>-9,7%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-20,38%</t>
+          <t>-16,7%</t>
         </is>
       </c>
     </row>
@@ -1647,54 +1647,54 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>12,95; 159,56</t>
+          <t>11,81; 162,77</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-43,77; 44,64</t>
+          <t>-45,85; 47,58</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-50,66; 22,81</t>
+          <t>-53,78; 17,99</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>17,17; 99,35</t>
+          <t>18,95; 105,49</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-36,76; 19,09</t>
+          <t>-35,4; 20,19</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-43,27; 5,54</t>
+          <t>-31,42; 15,65</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>24,26; 90,67</t>
+          <t>24,56; 93,19</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-33,77; 7,87</t>
+          <t>-34,18; 10,79</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-40,39; 2,62</t>
+          <t>-33,47; 4,11</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1,02</t>
+          <t>1,22</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-5,45</t>
+          <t>-5,46</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-5,07</t>
+          <t>-4,71</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 5,81</t>
+          <t>-0,05; 5,77</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0,15; 6,36</t>
+          <t>-0,05; 6,27</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 4,71</t>
+          <t>-1,25; 5,51</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-3,32; 4,12</t>
+          <t>-3,62; 4,49</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-10,89; -3,18</t>
+          <t>-10,83; -3,14</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-8,89; -2,07</t>
+          <t>-8,95; -1,85</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 3,81</t>
+          <t>-2,96; 3,84</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-8,88; -2,41</t>
+          <t>-8,98; -2,68</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-8,18; -2,38</t>
+          <t>-7,53; -1,49</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>77,81%</t>
+          <t>92,91%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-24,33%</t>
+          <t>-24,39%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-27,36%</t>
+          <t>-25,41%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-38,37; —</t>
+          <t>-31,11; 1343,94</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-30,36; 1415,32</t>
+          <t>-35,07; —</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-85,53; —</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-14,17; 20,11</t>
+          <t>-15,26; 21,07</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-45,93; -15,3</t>
+          <t>-43,96; -14,29</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-35,84; -9,96</t>
+          <t>-36,05; -8,97</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-14,08; 22,59</t>
+          <t>-14,86; 22,76</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-44,38; -15,07</t>
+          <t>-45,16; -16,08</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-39,85; -13,68</t>
+          <t>-37,61; -8,89</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-4,01</t>
+          <t>-3,18</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-5,05</t>
+          <t>-4,08</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-4,58</t>
+          <t>-3,67</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 3,42</t>
+          <t>-0,47; 3,44</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-4,93; -1,07</t>
+          <t>-4,97; -1,37</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-6,47; -2,14</t>
+          <t>-4,96; -1,53</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 3,98</t>
+          <t>0,11; 4,17</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-6,45; -2,73</t>
+          <t>-6,51; -2,71</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-7,4; -3,2</t>
+          <t>-5,87; -2,45</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,29; 3,15</t>
+          <t>0,33; 3,19</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-5,09; -2,46</t>
+          <t>-5,05; -2,3</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-6,3; -3,32</t>
+          <t>-4,87; -2,58</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-29,49%</t>
+          <t>-23,38%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-31,28%</t>
+          <t>-25,29%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-30,63%</t>
+          <t>-24,6%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-5,18; 27,07</t>
+          <t>-3,15; 27,52</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-32,92; -8,52</t>
+          <t>-33,72; -10,49</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-45,79; -17,26</t>
+          <t>-33,67; -12,03</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 26,01</t>
+          <t>0,53; 26,84</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-37,53; -17,9</t>
+          <t>-37,51; -17,54</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-44,24; -21,25</t>
+          <t>-33,71; -16,31</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>1,72; 22,16</t>
+          <t>2,16; 22,58</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-32,48; -17,3</t>
+          <t>-32,47; -16,26</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-40,97; -23,22</t>
+          <t>-31,27; -18,15</t>
         </is>
       </c>
     </row>
